--- a/files/me-ADPER0000094929.xlsx
+++ b/files/me-ADPER0000094929.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -561,7 +561,9 @@
           <t>주저자</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -606,7 +608,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -614,7 +616,9 @@
           <t>주저자</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
@@ -659,7 +663,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +671,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
@@ -712,7 +718,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -720,7 +726,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -728,44 +736,42 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>YOLO v2를 이용한 고해상도 항공영상에서의 태양광발전소 탐지 방법 연구</t>
+          <t>Transboundary water-food nexus based on physical-virtual water embedded in food trade network</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>김하영, 나라, 주동혁, 최규훈, 오윤경</t>
+          <t>Sang‐Hyun Lee, Makoto Taniguchi, Naoki Masuhara, Seung‐Hwan Yoo, Yun‐Gyeong Oh, Masahiko Haraguchi, Rui Qu</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Journal of Hydrology</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87-96</t>
+          <t>129819</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2022.28.2.087</t>
+          <t>10.1016/j.jhydrol.2023.129819</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -773,7 +779,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -781,16 +789,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>고해상도 농경지 데이터를 이용한 비료사용 농경지의 암모니아 배출량의 시공간적 변화 분석</t>
+          <t>YOLO v2를 이용한 고해상도 항공영상에서의 태양광발전소 탐지 방법 연구</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>박진선, 이세연, 홍세운, 나라, 오윤경</t>
+          <t>김하영, 나라, 주동혁, 최규훈, 오윤경</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -799,26 +807,26 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33-41</t>
+          <t>87-96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2021.27.4.033</t>
+          <t>10.7851/ksrp.2022.28.2.087</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -826,7 +834,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -838,40 +848,38 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>공간규모별 어촌지역 진단지표 개발</t>
+          <t>Vulnerability assessment of rural aging community for abandoned farmlands in South Korea</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>조은정, 오윤경, 배승종, 김수진, 이상현</t>
+          <t>Jimin Lee, Yun‐Gyeong Oh, Seung‐Hwan Yoo, Kyo Suh</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Land Use Policy</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9-20</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2021.27.1.009</t>
+          <t>10.1016/j.landusepol.2021.105544</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -879,7 +887,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="n">
+        <v>56</v>
+      </c>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -887,16 +897,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>가뭄 대응형 지하수 개발 우선순위 선정을 위한 농촌용수구역의 유형 분석</t>
+          <t>고해상도 농경지 데이터를 이용한 비료사용 농경지의 암모니아 배출량의 시공간적 변화 분석</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 이상현, 김아라, 홍순욱, 유승환</t>
+          <t>박진선, 이세연, 홍세운, 나라, 오윤경</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -905,34 +915,36 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51-59</t>
+          <t>33-41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10.7851/Ksrp.2020.26.2.051</t>
+          <t>10.7851/ksrp.2021.27.4.033</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
@@ -940,16 +952,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>융복합 농산업화 모델 유형별 잠재가능성 분석 - 밭작물 주산단지를 중심으로 -</t>
+          <t>공간규모별 어촌지역 진단지표 개발</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>이상현, 김윤형, 배승종, 서동욱, 오윤경</t>
+          <t>조은정, 오윤경, 배승종, 김수진, 이상현</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -958,26 +970,26 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25-37</t>
+          <t>9-20</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10.7851/Ksrp.2020.26.2.025</t>
+          <t>10.7851/ksrp.2021.27.1.009</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -985,7 +997,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
@@ -993,25 +1007,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보를 활용한 밭 경작지의 공간적 파편화 특성 분석</t>
+          <t>가뭄 대응형 지하수 개발 우선순위 선정을 위한 농촌용수구역의 유형 분석</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>이지민, 유승환, 오윤경</t>
+          <t>오윤경, 이상현, 김아라, 홍순욱, 유승환</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1020,25 +1034,27 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13-24</t>
+          <t>51-59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.2.013</t>
+          <t>10.7851/Ksrp.2020.26.2.051</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1046,52 +1062,54 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>농업경영체 등록정보와 공간데이터를 활용한 밭 이용 방안 연구: 전라남도 무안군·해남군을 중심으로</t>
+          <t>융복합 농산업화 모델 유형별 잠재가능성 분석 - 밭작물 주산단지를 중심으로 -</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 유승환, 최수명, 이지민</t>
+          <t>이상현, 김윤형, 배승종, 서동욱, 오윤경</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27-35</t>
+          <t>25-37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.4.027</t>
+          <t>10.7851/Ksrp.2020.26.2.025</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1099,52 +1117,54 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>지형 특성과 경작지 분포를 고려한 밭정비 유형 분석 - 무안군과 화순군 비교 -</t>
+          <t>Comparative analysis of the theoretical–technical potential of rice straw bioenergy in South Korea</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>이지민, 유승환, 오윤경, 김아라</t>
+          <t>Jimin Lee, Yun‐Gyeong Oh</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>Paddy and Water Environment</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>133-144</t>
+          <t>455-462</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2018.60.6.133</t>
+          <t>10.1007/s10333-019-00741-2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1152,52 +1172,52 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>경관지수를 활용한 채소 주산지 공간적 분포 특성 분석</t>
+          <t>Participation Survey of Demonstration Projects for Integrated and Comprehensive Agricultural Industry in the Main Production Areas</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>배승종, 김대식, 김수진, 오윤경</t>
+          <t>Ara Kim, Eun‐Jung Cho, Sang-Hyun Lee, Jimin Lee, Yun‐Gyeong Oh</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Trends in Agriculture &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>135-146</t>
+          <t>43-47</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10.7851/ksrp.2017.23.1.135</t>
+          <t>10.29335/tals.2019.57.43</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>국내 기타</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>교신저자</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1205,44 +1225,44 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>지역 간 시계열 인구이동의 정량적 특징 분석 및 인구이동 네트워크의 연결중심성 분석</t>
+          <t>Analyzing characteristics and centralities of the Agricultural Products Networks</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>이상현, 오윤경</t>
+          <t>Jimin Lee, Yun‐Gyeong Oh</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>국토계획</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1-15</t>
+          <t>105-122</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2017.59.5.001</t>
+          <t>10.17208/jkpa.2018.02.53.1.105</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1250,7 +1270,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1258,16 +1280,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RapidEye 위성영상의 시계열 NDVI 및 객체기반 분류를 이용한 북한 재령군의 논벼 재배지역 추출 기법 연구</t>
+          <t>농업경영체 등록정보를 활용한 밭 경작지의 공간적 파편화 특성 분석</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>이상현, 오윤경, 박나영, 이성학, 최진용</t>
+          <t>이지민, 유승환, 오윤경</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1276,26 +1298,26 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>13-24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2014.56.3.055</t>
+          <t>10.5389/KSAE.2018.60.2.013</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1311,16 +1333,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>고해상도 기후시나리오를 이용한 논용수 수요량 및 단위용수량의 기후변화 영향 분석</t>
+          <t>농업경영체 등록정보와 공간데이터를 활용한 밭 이용 방안 연구: 전라남도 무안군·해남군을 중심으로</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>유승환, 최진용, 이상현, 오윤경, 박나영</t>
+          <t>오윤경, 유승환, 최수명, 이지민</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1329,34 +1351,36 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15-26</t>
+          <t>27-35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.2.015</t>
+          <t>10.5389/KSAE.2018.60.4.027</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>공저자</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1364,16 +1388,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오 (A1B)에 따른 농업용 저수지 유역의 미래 토지피복변화 예측 및 논 면적 변화 특성 분석</t>
+          <t>지형 특성과 경작지 분포를 고려한 밭정비 유형 분석 - 무안군과 화순군 비교 -</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 유승환, 이상현, 박나영, 최진용, 윤동균</t>
+          <t>이지민, 유승환, 오윤경, 김아라</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1382,31 +1406,31 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77-86</t>
+          <t>133-144</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.2.077</t>
+          <t>10.5389/KSAE.2018.60.6.133</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
+          <t>공저자</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1417,25 +1441,25 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오에 따른 미래 논벼의 소비수량 및 생산량 변화 분석</t>
+          <t>경관지수를 활용한 채소 주산지 공간적 분포 특성 분석</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>이태석, 최진용, 유승환, 이상현, 오윤경</t>
+          <t>배승종, 김대식, 김수진, 오윤경</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>한국농공학회논문집</t>
+          <t>농촌계획</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1444,17 +1468,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47-54</t>
+          <t>135-146</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2012.54.1.047</t>
+          <t>10.7851/ksrp.2017.23.1.135</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1462,7 +1486,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1470,16 +1496,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>기후변화 시나리오에 따른 미래 토지피복변화 예측 및 군집분석을 이용한 지역 특성 분석</t>
+          <t>지역 간 시계열 인구이동의 정량적 특징 분석 및 인구이동 네트워크의 연결중심성 분석</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 유승환, 이상현</t>
+          <t>이상현, 오윤경</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1488,34 +1514,36 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31-41</t>
+          <t>1-15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2011.53.6.031</t>
+          <t>10.5389/KSAE.2017.59.5.001</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1523,25 +1551,25 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>농촌지역개발컨설팅에 있어서 농촌어메니티 자원정보 요구분석</t>
+          <t>RapidEye 위성영상의 시계열 NDVI 및 객체기반 분류를 이용한 북한 재령군의 논벼 재배지역 추출 기법 연구</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>배승종, 최진용, 오윤경, 양용석</t>
+          <t>이상현, 오윤경, 박나영, 이성학, 최진용</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1550,13 +1578,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77-85</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr"/>
+          <t>55-64</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2014.56.3.055</t>
+        </is>
+      </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1564,7 +1596,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1572,40 +1606,42 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>지니계수를 통한 농촌어메니티 자원 집중화 연구</t>
+          <t>Climate change impacts on water storage requirements of an agricultural reservoir considering changes in land use and rice growing season in Korea</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>이상현, 최진용, 오윤경, 배승종</t>
+          <t>Yoo Seung-Hwan, Jin‐Yong Choi, Sang‐Hyun Lee, Yun‐Gyeong Oh, Yun Dong Koun</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Agricultural Water Management</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57-64</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>43-54</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.agwat.2012.10.023</t>
+        </is>
+      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1613,7 +1649,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="n">
+        <v>54</v>
+      </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1621,48 +1659,52 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>토지피복변화 예측을 위한 CLUE 모델의 확률지도 생성</t>
+          <t>Evaluating spatial centrality for integrated tourism management in rural areas using GIS and network analysis</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 배승종, 유승환, 이상현</t>
+          <t>Sang-Hyun Lee, Jin‐Yong Choi, Seung-Hwan Yoo, Yun‐Gyeong Oh</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Tourism Management</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47-55</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>14-24</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.tourman.2012.03.005</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>해외</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>144</v>
+      </c>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1670,40 +1712,44 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>GIS 및 사회네트워크 분석을 통한 농촌마을 관광중심성 분석 -농촌어메니티 자원 및 인적자원을 중심으로-</t>
+          <t>고해상도 기후시나리오를 이용한 논용수 수요량 및 단위용수량의 기후변화 영향 분석</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>이상현, 최진용, 배승종, 오윤경</t>
+          <t>유승환, 최진용, 이상현, 오윤경, 박나영</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47-59</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>15-26</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.2.015</t>
+        </is>
+      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1711,7 +1757,9 @@
           <t>공저자</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1719,40 +1767,44 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>농촌어메니티 자원도 활용방안 모색을 위한 수요자 요구조사</t>
+          <t>기후변화 시나리오 (A1B)에 따른 농업용 저수지 유역의 미래 토지피복변화 예측 및 논 면적 변화 특성 분석</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 이지민, 배승종</t>
+          <t>오윤경, 유승환, 이상현, 박나영, 최진용, 윤동균</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1-10</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>77-86</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.2.077</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1760,7 +1812,9 @@
           <t>주저자</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1768,48 +1822,54 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>생활 및 관광자원으로서의 특성을 고려한 농촌어메니티의 지역별 수준평가</t>
+          <t>기후변화 시나리오에 따른 미래 논벼의 소비수량 및 생산량 변화 분석</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 배승종</t>
+          <t>이태석, 최진용, 유승환, 이상현, 오윤경</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>농촌계획</t>
+          <t>한국농공학회논문집</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21-32</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t>47-54</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2012.54.1.047</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>주저자</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1817,16 +1877,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>경관생태지수를 활용한 농촌경관의 시계열적 변화 분석 - 경기도 일부 시.군을 대상으로 -</t>
+          <t>기후변화 시나리오에 따른 미래 토지피복변화 예측 및 군집분석을 이용한 지역 특성 분석</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>오윤경, 최진용, 배승종, 장민원</t>
+          <t>오윤경, 최진용, 유승환, 이상현</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1835,7 +1895,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1844,17 +1904,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>65-76</t>
+          <t>31-41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10.5389/KSAE.2007.49.6.065</t>
+          <t>10.5389/KSAE.2011.53.6.031</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>세 학회지</t>
+          <t>수집 학회지</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1862,7 +1922,9 @@
           <t>주저자</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1870,49 +1932,455 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Prediction of paddy field change based on climate change scenarios using the CLUE model</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Yun‐Gyeong Oh, Seung‐Hwan Yoo, Sang‐Hyun Lee, Jin‐Yong Choi</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Paddy and Water Environment</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>309-323</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/s10333-010-0244-0</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>농촌지역개발컨설팅에 있어서 농촌어메니티 자원정보 요구분석</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>배승종, 최진용, 오윤경, 양용석</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>77-85</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>지니계수를 통한 농촌어메니티 자원 집중화 연구</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>이상현, 최진용, 오윤경, 배승종</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>57-64</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>토지피복변화 예측을 위한 CLUE 모델의 확률지도 생성</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>오윤경, 최진용, 배승종, 유승환, 이상현</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>47-55</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GIS 및 사회네트워크 분석을 통한 농촌마을 관광중심성 분석 -농촌어메니티 자원 및 인적자원을 중심으로-</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>이상현, 최진용, 배승종, 오윤경</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>47-59</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>공저자</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>농촌어메니티 자원도 활용방안 모색을 위한 수요자 요구조사</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>오윤경, 최진용, 이지민, 배승종</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>1-10</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>생활 및 관광자원으로서의 특성을 고려한 농촌어메니티의 지역별 수준평가</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>오윤경, 최진용, 배승종</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>농촌계획</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>21-32</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="n">
         <v>2007</v>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>경관생태지수를 활용한 농촌경관의 시계열적 변화 분석 - 경기도 일부 시.군을 대상으로 -</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>오윤경, 최진용, 배승종, 장민원</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>한국농공학회논문집</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>65-76</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>10.5389/KSAE.2007.49.6.065</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>주저자</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>농촌어메니티 자원조사 연구</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>오윤경, 조순재, 최진용, 임승빈, 안동만, 이정재, 이동근</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>농촌계획</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="F36" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>1-9</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>세 학회지</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>수집 학회지</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>주저자</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/files/me-ADPER0000094929.xlsx
+++ b/files/me-ADPER0000094929.xlsx
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
